--- a/artfynd/A 46706-2024 artfynd.xlsx
+++ b/artfynd/A 46706-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121328851</v>
       </c>
       <c r="B2" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121328849</v>
+        <v>121328850</v>
       </c>
       <c r="B3" t="n">
-        <v>57499</v>
+        <v>57504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121328850</v>
+        <v>121328849</v>
       </c>
       <c r="B4" t="n">
-        <v>57501</v>
+        <v>57502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,21 +931,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">

--- a/artfynd/A 46706-2024 artfynd.xlsx
+++ b/artfynd/A 46706-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121328851</v>
+        <v>121328850</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>57504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121328850</v>
+        <v>121328849</v>
       </c>
       <c r="B3" t="n">
-        <v>57504</v>
+        <v>57502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121328849</v>
+        <v>121328851</v>
       </c>
       <c r="B4" t="n">
-        <v>57502</v>
+        <v>57720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,20 +927,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 46706-2024 artfynd.xlsx
+++ b/artfynd/A 46706-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121328850</v>
+        <v>121328849</v>
       </c>
       <c r="B2" t="n">
-        <v>57504</v>
+        <v>57502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121328849</v>
+        <v>121328851</v>
       </c>
       <c r="B3" t="n">
-        <v>57502</v>
+        <v>57720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,20 +807,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121328851</v>
+        <v>121328850</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>57504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,30 +927,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 46706-2024 artfynd.xlsx
+++ b/artfynd/A 46706-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121328851</v>
+        <v>121328850</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,30 +807,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121328850</v>
+        <v>121328851</v>
       </c>
       <c r="B4" t="n">
-        <v>57504</v>
+        <v>57720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,30 +927,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 46706-2024 artfynd.xlsx
+++ b/artfynd/A 46706-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121328849</v>
+        <v>121328851</v>
       </c>
       <c r="B2" t="n">
-        <v>57502</v>
+        <v>57723</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -798,7 +798,7 @@
         <v>121328850</v>
       </c>
       <c r="B3" t="n">
-        <v>57504</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121328851</v>
+        <v>121328849</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>57505</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,20 +927,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 46706-2024 artfynd.xlsx
+++ b/artfynd/A 46706-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121328851</v>
+        <v>121328850</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>57508</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121328850</v>
+        <v>121328849</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>57506</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121328849</v>
+        <v>121328851</v>
       </c>
       <c r="B4" t="n">
-        <v>57505</v>
+        <v>57724</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,20 +927,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 46706-2024 artfynd.xlsx
+++ b/artfynd/A 46706-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121328850</v>
+        <v>121328851</v>
       </c>
       <c r="B2" t="n">
-        <v>57508</v>
+        <v>57725</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121328849</v>
+        <v>121328850</v>
       </c>
       <c r="B3" t="n">
-        <v>57506</v>
+        <v>57509</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121328851</v>
+        <v>121328849</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,20 +927,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 46706-2024 artfynd.xlsx
+++ b/artfynd/A 46706-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121328850</v>
+        <v>121328849</v>
       </c>
       <c r="B3" t="n">
-        <v>57509</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121328849</v>
+        <v>121328850</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>57509</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,21 +931,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">

--- a/artfynd/A 46706-2024 artfynd.xlsx
+++ b/artfynd/A 46706-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121328851</v>
+        <v>121328849</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121328849</v>
+        <v>121328850</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>57509</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121328850</v>
+        <v>121328851</v>
       </c>
       <c r="B4" t="n">
-        <v>57509</v>
+        <v>57725</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,30 +927,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 46706-2024 artfynd.xlsx
+++ b/artfynd/A 46706-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121328849</v>
+        <v>121328851</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>57725</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121328850</v>
+        <v>121328849</v>
       </c>
       <c r="B3" t="n">
-        <v>57509</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121328851</v>
+        <v>121328850</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>57509</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,30 +927,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 46706-2024 artfynd.xlsx
+++ b/artfynd/A 46706-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121328851</v>
+        <v>121328850</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
+        <v>57510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -798,7 +798,7 @@
         <v>121328849</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>57508</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121328850</v>
+        <v>121328851</v>
       </c>
       <c r="B4" t="n">
-        <v>57509</v>
+        <v>57726</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,30 +927,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
